--- a/sequence-generator/Book1.xlsx
+++ b/sequence-generator/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1895b5d248d78747/Documents/Code/GLSL/rutt-etra-app/sequence-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{4F8526F2-5DF1-C544-9847-B895B58EDC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{783D9E89-EDD5-574E-866D-436ADF792DCC}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{4F8526F2-5DF1-C544-9847-B895B58EDC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C318D77-F465-A14D-89C0-DB4C738F1F73}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="1420" windowWidth="27640" windowHeight="16940" xr2:uid="{15FA9194-8FE4-3D42-8AD7-5CA4CF0CDB18}"/>
+    <workbookView xWindow="41820" yWindow="2460" windowWidth="27640" windowHeight="16940" xr2:uid="{15FA9194-8FE4-3D42-8AD7-5CA4CF0CDB18}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -555,7 +555,7 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O2">
         <v>1.1000000000000001</v>
@@ -574,43 +574,43 @@
       </c>
       <c r="B3">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-45</v>
+        <v>50</v>
       </c>
       <c r="C3">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-56</v>
+        <v>66</v>
       </c>
       <c r="D3">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="E3">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="F3">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-3</v>
+        <v>-15</v>
       </c>
       <c r="H3">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="J3">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K3">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O3">
         <v>1.1000000000000001</v>
@@ -673,7 +673,7 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O4">
         <v>1.1000000000000001</v>
@@ -692,11 +692,11 @@
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="D5">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
@@ -704,7 +704,7 @@
       </c>
       <c r="E5">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
@@ -712,23 +712,23 @@
       </c>
       <c r="G5">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="H5">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J5">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K5">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O5">
         <v>1.1000000000000001</v>
@@ -791,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O6">
         <v>1.1000000000000001</v>
@@ -810,35 +810,35 @@
       </c>
       <c r="B7">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-28</v>
+        <v>-59</v>
       </c>
       <c r="C7">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-86</v>
+        <v>143</v>
       </c>
       <c r="D7">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="E7">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="F7">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-5</v>
+        <v>13</v>
       </c>
       <c r="G7">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="I7">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
@@ -846,7 +846,7 @@
       </c>
       <c r="K7">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O7">
         <v>1.1000000000000001</v>
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O8">
         <v>1.1000000000000001</v>
@@ -928,43 +928,43 @@
       </c>
       <c r="B9">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>147</v>
+        <v>67</v>
       </c>
       <c r="E9">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F9">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H9">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>6</v>
+        <v>-17</v>
       </c>
       <c r="I9">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-13</v>
+        <v>-17</v>
       </c>
       <c r="J9">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K9">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
         <v>1.1000000000000001</v>
@@ -992,43 +992,43 @@
       </c>
       <c r="B10">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>76</v>
+        <v>-62</v>
       </c>
       <c r="C10">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-129</v>
+        <v>-67</v>
       </c>
       <c r="D10">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="F10">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="G10">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-12</v>
+        <v>12</v>
       </c>
       <c r="I10">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="K10">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O10">
         <v>1.1000000000000001</v>
@@ -1091,7 +1091,7 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O11">
         <v>1.1000000000000001</v>
@@ -1110,39 +1110,39 @@
       </c>
       <c r="B12">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-9</v>
+        <v>-39</v>
       </c>
       <c r="C12">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="E12">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="F12">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>2</v>
+        <v>-13</v>
       </c>
       <c r="G12">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I12">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K12">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O12">
         <v>1.1000000000000001</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O13">
         <v>1.1000000000000001</v>
@@ -1228,23 +1228,23 @@
       </c>
       <c r="B14">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C14">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>107</v>
+        <v>-148</v>
       </c>
       <c r="D14">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E14">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="F14">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
@@ -1252,19 +1252,19 @@
       </c>
       <c r="H14">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>12</v>
+        <v>-11</v>
       </c>
       <c r="I14">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>19</v>
+        <v>-20</v>
       </c>
       <c r="J14">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K14">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O14">
         <v>1.1000000000000001</v>
@@ -1292,43 +1292,43 @@
       </c>
       <c r="B15">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-6</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-76</v>
+        <v>86</v>
       </c>
       <c r="D15">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="E15">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="G15">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>14</v>
+        <v>-15</v>
       </c>
       <c r="H15">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-15</v>
+        <v>-4</v>
       </c>
       <c r="I15">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="J15">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K15">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.3</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O15">
         <v>1.1000000000000001</v>
@@ -1356,43 +1356,43 @@
       </c>
       <c r="B16">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-47</v>
+        <v>-32</v>
       </c>
       <c r="C16">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>99</v>
+        <v>165</v>
       </c>
       <c r="D16">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="E16">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="F16">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-3</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H16">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="I16">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>16</v>
+        <v>-14</v>
       </c>
       <c r="J16">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K16">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O16">
         <v>1.1000000000000001</v>
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O17">
         <v>1.1000000000000001</v>
@@ -1474,43 +1474,43 @@
       </c>
       <c r="B18">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="C18">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>99</v>
+        <v>-147</v>
       </c>
       <c r="D18">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E18">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="G18">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="H18">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="I18">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="J18">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K18">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
         <v>1.1000000000000001</v>
@@ -1538,35 +1538,35 @@
       </c>
       <c r="B19">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>44</v>
+        <v>-24</v>
       </c>
       <c r="C19">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="E19">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-13</v>
+        <v>2</v>
       </c>
       <c r="H19">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-1</v>
+        <v>-17</v>
       </c>
       <c r="I19">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="K19">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O19">
         <v>1.1000000000000001</v>
@@ -1602,43 +1602,43 @@
       </c>
       <c r="B20">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>35</v>
+        <v>-66</v>
       </c>
       <c r="C20">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-151</v>
+        <v>-121</v>
       </c>
       <c r="D20">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="F20">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>9</v>
+        <v>-8</v>
       </c>
       <c r="G20">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="I20">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="J20">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K20">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O20">
         <v>1.1000000000000001</v>
@@ -1666,35 +1666,35 @@
       </c>
       <c r="B21">
         <f t="shared" ref="B21:B29" ca="1" si="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-49</v>
+        <v>-70</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:C29" ca="1" si="2">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-165</v>
+        <v>54</v>
       </c>
       <c r="D21">
         <f t="shared" ref="D21:D29" ca="1" si="3">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="E21">
         <f t="shared" ref="E21:E29" ca="1" si="4">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F21">
         <f t="shared" ref="F21:F29" ca="1" si="5">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="G21">
         <f t="shared" ref="G21:G29" ca="1" si="6">RANDBETWEEN($G$32,$G$33)</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H21">
         <f t="shared" ref="H21:H29" ca="1" si="7">RANDBETWEEN($H$32,$H$33)</f>
-        <v>8</v>
+        <v>-13</v>
       </c>
       <c r="I21">
         <f t="shared" ref="I21:I29" ca="1" si="8">RANDBETWEEN($I$32,$I$33)</f>
-        <v>17</v>
+        <v>-18</v>
       </c>
       <c r="J21">
         <f t="shared" ref="J21:J29" ca="1" si="9">RANDBETWEEN($J$32,$J$33)/10</f>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="K21">
         <f t="shared" ref="K21:K29" ca="1" si="10">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1711,7 +1711,7 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O21">
         <v>1.1000000000000001</v>
@@ -1730,43 +1730,43 @@
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>-74</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="2"/>
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="3"/>
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="4"/>
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="5"/>
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <f t="shared" ca="1" si="6"/>
-        <v>13</v>
+        <v>-11</v>
       </c>
       <c r="H22">
         <f t="shared" ca="1" si="7"/>
-        <v>4</v>
+        <v>-18</v>
       </c>
       <c r="I22">
         <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>-8</v>
       </c>
       <c r="J22">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="10"/>
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O22">
         <v>1.1000000000000001</v>
@@ -1794,27 +1794,27 @@
       </c>
       <c r="B23">
         <f t="shared" ca="1" si="1"/>
-        <v>41</v>
+        <v>-78</v>
       </c>
       <c r="C23">
         <f t="shared" ca="1" si="2"/>
-        <v>-5</v>
+        <v>-138</v>
       </c>
       <c r="D23">
         <f t="shared" ca="1" si="3"/>
-        <v>53</v>
+        <v>168</v>
       </c>
       <c r="E23">
         <f t="shared" ca="1" si="4"/>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F23">
         <f t="shared" ca="1" si="5"/>
-        <v>3</v>
+        <v>-12</v>
       </c>
       <c r="G23">
         <f t="shared" ca="1" si="6"/>
-        <v>-3</v>
+        <v>14</v>
       </c>
       <c r="H23">
         <f t="shared" ca="1" si="7"/>
@@ -1822,15 +1822,15 @@
       </c>
       <c r="I23">
         <f t="shared" ca="1" si="8"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J23">
         <f t="shared" ca="1" si="9"/>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K23">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O23">
         <v>1.1000000000000001</v>
@@ -1858,35 +1858,35 @@
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>-46</v>
+        <v>18</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="2"/>
-        <v>85</v>
+        <v>-71</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="3"/>
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="4"/>
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="5"/>
-        <v>15</v>
+        <v>-8</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
-        <v>-19</v>
+        <v>-4</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="8"/>
-        <v>-19</v>
+        <v>12</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="9"/>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="10"/>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O24">
         <v>1.1000000000000001</v>
@@ -1922,43 +1922,43 @@
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="1"/>
-        <v>-57</v>
+        <v>-4</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="2"/>
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="3"/>
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="4"/>
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="5"/>
-        <v>14</v>
+        <v>-15</v>
       </c>
       <c r="G25">
         <f t="shared" ca="1" si="6"/>
-        <v>6</v>
+        <v>-12</v>
       </c>
       <c r="H25">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="I25">
         <f t="shared" ca="1" si="8"/>
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="J25">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="10"/>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1967,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O25">
         <v>1.1000000000000001</v>
@@ -1986,43 +1986,43 @@
       </c>
       <c r="B26">
         <f t="shared" ca="1" si="1"/>
-        <v>-67</v>
+        <v>44</v>
       </c>
       <c r="C26">
         <f t="shared" ca="1" si="2"/>
-        <v>114</v>
+        <v>-67</v>
       </c>
       <c r="D26">
         <f t="shared" ca="1" si="3"/>
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="E26">
         <f t="shared" ca="1" si="4"/>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
         <f t="shared" ca="1" si="5"/>
-        <v>4</v>
+        <v>-12</v>
       </c>
       <c r="G26">
         <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="H26">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>-20</v>
       </c>
       <c r="I26">
         <f t="shared" ca="1" si="8"/>
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="J26">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K26">
         <f t="shared" ca="1" si="10"/>
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O26">
         <v>1.1000000000000001</v>
@@ -2050,43 +2050,43 @@
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="1"/>
-        <v>-34</v>
+        <v>-76</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="2"/>
-        <v>170</v>
+        <v>-143</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="3"/>
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="5"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="6"/>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
-        <v>-20</v>
+        <v>-12</v>
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="10"/>
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O27">
         <v>1.1000000000000001</v>
@@ -2114,39 +2114,39 @@
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="1"/>
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="2"/>
-        <v>-35</v>
+        <v>-155</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="3"/>
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="4"/>
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F28">
         <f t="shared" ca="1" si="5"/>
-        <v>11</v>
+        <v>-3</v>
       </c>
       <c r="G28">
         <f t="shared" ca="1" si="6"/>
-        <v>12</v>
+        <v>-15</v>
       </c>
       <c r="H28">
         <f t="shared" ca="1" si="7"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I28">
         <f t="shared" ca="1" si="8"/>
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="J28">
         <f t="shared" ca="1" si="9"/>
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="10"/>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O28">
         <v>1.1000000000000001</v>
@@ -2178,43 +2178,43 @@
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="1"/>
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="2"/>
-        <v>-82</v>
+        <v>-150</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="3"/>
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="4"/>
-        <v>1.1000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F29">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>-14</v>
       </c>
       <c r="G29">
         <f t="shared" ca="1" si="6"/>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H29">
         <f t="shared" ca="1" si="7"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I29">
         <f t="shared" ca="1" si="8"/>
-        <v>6</v>
+        <v>-18</v>
       </c>
       <c r="J29">
         <f t="shared" ca="1" si="9"/>
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K29">
         <f t="shared" ca="1" si="10"/>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O29">
         <v>1.1000000000000001</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O30">
         <v>1.1000000000000001</v>

--- a/sequence-generator/Book1.xlsx
+++ b/sequence-generator/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1895b5d248d78747/Documents/Code/GLSL/rutt-etra-app/sequence-generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{4F8526F2-5DF1-C544-9847-B895B58EDC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C318D77-F465-A14D-89C0-DB4C738F1F73}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{4F8526F2-5DF1-C544-9847-B895B58EDC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9549499F-2D9F-E444-BA9F-9CB82D0EE16C}"/>
   <bookViews>
     <workbookView xWindow="41820" yWindow="2460" windowWidth="27640" windowHeight="16940" xr2:uid="{15FA9194-8FE4-3D42-8AD7-5CA4CF0CDB18}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>time</t>
   </si>
@@ -87,6 +87,15 @@
   </si>
   <si>
     <t>temporalDecay</t>
+  </si>
+  <si>
+    <t>EdgeThresh</t>
+  </si>
+  <si>
+    <t>NormEdgeSt</t>
+  </si>
+  <si>
+    <t>DepEdgeSt</t>
   </si>
 </sst>
 </file>
@@ -458,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{895A3A9E-3D9C-3F4C-B24C-F61B7F23052B}">
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -513,8 +522,17 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -555,62 +573,71 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>1.1000000000000001</v>
       </c>
       <c r="P2">
+        <v>0.8</v>
+      </c>
+      <c r="Q2">
+        <v>1.2</v>
+      </c>
+      <c r="S2">
+        <v>0.11</v>
+      </c>
+      <c r="T2">
         <v>0.1</v>
       </c>
-      <c r="Q2">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="U2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3">
-        <f>A2+6000</f>
-        <v>6000</v>
+        <f>A2+$A$32</f>
+        <v>8250</v>
       </c>
       <c r="B3">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>50</v>
+        <v>-24</v>
       </c>
       <c r="C3">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>66</v>
+        <v>-77</v>
       </c>
       <c r="D3">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="E3">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="F3">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="H3">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="I3">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K3">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -619,22 +646,22 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O3">
         <v>1.1000000000000001</v>
       </c>
       <c r="P3">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4">
-        <f t="shared" ref="A4:A30" si="0">A3+6000</f>
-        <v>12000</v>
+        <f t="shared" ref="A4:A30" si="0">A3+$A$32</f>
+        <v>16500</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -673,62 +700,62 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.1000000000000001</v>
       </c>
       <c r="P4">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q4">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5">
         <f t="shared" si="0"/>
-        <v>18000</v>
+        <v>24750</v>
       </c>
       <c r="B5">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="C5">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D5">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E5">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="F5">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-8</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="H5">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>17</v>
+        <v>-5</v>
       </c>
       <c r="J5">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -737,22 +764,22 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>1.1000000000000001</v>
       </c>
       <c r="P5">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q5">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6">
         <f t="shared" si="0"/>
-        <v>24000</v>
+        <v>33000</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -791,62 +818,62 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O6">
         <v>1.1000000000000001</v>
       </c>
       <c r="P6">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7">
         <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>41250</v>
       </c>
       <c r="B7">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-59</v>
+        <v>14</v>
       </c>
       <c r="C7">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>143</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="E7">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F7">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G7">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="H7">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="I7">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>13</v>
+        <v>-8</v>
       </c>
       <c r="J7">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="K7">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -855,22 +882,22 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O7">
         <v>1.1000000000000001</v>
       </c>
       <c r="P7">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
-        <v>36000</v>
+        <v>49500</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -909,62 +936,62 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>1.1000000000000001</v>
       </c>
       <c r="P8">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q8">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
-        <v>42000</v>
+        <v>57750</v>
       </c>
       <c r="B9">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>110</v>
+        <v>-161</v>
       </c>
       <c r="D9">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="E9">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.7</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F9">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>15</v>
+        <v>-13</v>
       </c>
       <c r="G9">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="H9">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="I9">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="J9">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="K9">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -973,62 +1000,62 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O9">
         <v>1.1000000000000001</v>
       </c>
       <c r="P9">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q9">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="0"/>
-        <v>48000</v>
+        <v>66000</v>
       </c>
       <c r="B10">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-62</v>
+        <v>-57</v>
       </c>
       <c r="C10">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-67</v>
+        <v>-140</v>
       </c>
       <c r="D10">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E10">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="F10">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G10">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="H10">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="J10">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1037,22 +1064,22 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O10">
         <v>1.1000000000000001</v>
       </c>
       <c r="P10">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
-        <v>54000</v>
+        <v>74250</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1091,50 +1118,50 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O11">
         <v>1.1000000000000001</v>
       </c>
       <c r="P11">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q11">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="0"/>
-        <v>60000</v>
+        <v>82500</v>
       </c>
       <c r="B12">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-39</v>
+        <v>52</v>
       </c>
       <c r="C12">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="D12">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="F12">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-13</v>
+        <v>10</v>
       </c>
       <c r="G12">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="I12">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
@@ -1142,11 +1169,11 @@
       </c>
       <c r="J12">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -1155,22 +1182,22 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O12">
         <v>1.1000000000000001</v>
       </c>
       <c r="P12">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q12">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="0"/>
-        <v>66000</v>
+        <v>90750</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1209,34 +1236,34 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>1.1000000000000001</v>
       </c>
       <c r="P13">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q13">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="0"/>
-        <v>72000</v>
+        <v>99000</v>
       </c>
       <c r="B14">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>77</v>
+        <v>-49</v>
       </c>
       <c r="C14">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-148</v>
+        <v>94</v>
       </c>
       <c r="D14">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
@@ -1244,27 +1271,27 @@
       </c>
       <c r="F14">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G14">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-15</v>
+        <v>-7</v>
       </c>
       <c r="H14">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="I14">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-20</v>
+        <v>-6</v>
       </c>
       <c r="J14">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="K14">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -1273,54 +1300,54 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O14">
         <v>1.1000000000000001</v>
       </c>
       <c r="P14">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q14">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
-        <v>78000</v>
+        <v>107250</v>
       </c>
       <c r="B15">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>39</v>
+        <v>-32</v>
       </c>
       <c r="C15">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E15">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="F15">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-15</v>
+        <v>-6</v>
       </c>
       <c r="H15">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="J15">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
@@ -1328,7 +1355,7 @@
       </c>
       <c r="K15">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -1337,62 +1364,62 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O15">
         <v>1.1000000000000001</v>
       </c>
       <c r="P15">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q15">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
-        <v>84000</v>
+        <v>115500</v>
       </c>
       <c r="B16">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-32</v>
+        <v>-53</v>
       </c>
       <c r="C16">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="D16">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="E16">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.1</v>
+        <v>1.2</v>
       </c>
       <c r="F16">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>11</v>
+        <v>-6</v>
       </c>
       <c r="G16">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="H16">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="I16">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-14</v>
+        <v>4</v>
       </c>
       <c r="J16">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="K16">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1401,22 +1428,22 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O16">
         <v>1.1000000000000001</v>
       </c>
       <c r="P16">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q16">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="0"/>
-        <v>90000</v>
+        <v>123750</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1455,58 +1482,58 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O17">
         <v>1.1000000000000001</v>
       </c>
       <c r="P17">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q17">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="0"/>
-        <v>96000</v>
+        <v>132000</v>
       </c>
       <c r="B18">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-147</v>
+        <v>-163</v>
       </c>
       <c r="D18">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>141</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F18">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G18">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>-11</v>
+        <v>10</v>
       </c>
       <c r="H18">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-5</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="K18">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
@@ -1519,62 +1546,62 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O18">
         <v>1.1000000000000001</v>
       </c>
       <c r="P18">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q18">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="0"/>
-        <v>102000</v>
+        <v>140250</v>
       </c>
       <c r="B19">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-24</v>
+        <v>17</v>
       </c>
       <c r="C19">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>57</v>
+        <v>-45</v>
       </c>
       <c r="D19">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="E19">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="F19">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="H19">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="I19">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="J19">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K19">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1583,62 +1610,62 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O19">
         <v>1.1000000000000001</v>
       </c>
       <c r="P19">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q19">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="0"/>
-        <v>108000</v>
+        <v>148500</v>
       </c>
       <c r="B20">
         <f ca="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-66</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <f ca="1">RANDBETWEEN($C$32,$C$33)</f>
-        <v>-121</v>
+        <v>117</v>
       </c>
       <c r="D20">
         <f ca="1">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <f ca="1">RANDBETWEEN($E$32,$E$33)/10</f>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F20">
         <f ca="1">RANDBETWEEN($F$32,$F$33)</f>
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="G20">
         <f ca="1">RANDBETWEEN($G$32,$G$33)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H20">
         <f ca="1">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="I20">
         <f ca="1">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <f ca="1">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="K20">
         <f ca="1">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>1.1000000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1647,34 +1674,34 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>1.1000000000000001</v>
       </c>
       <c r="P20">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q20">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="0"/>
-        <v>114000</v>
+        <v>156750</v>
       </c>
       <c r="B21">
         <f t="shared" ref="B21:B29" ca="1" si="1">RANDBETWEEN($B$32,$B$33)</f>
-        <v>-70</v>
+        <v>-8</v>
       </c>
       <c r="C21">
         <f t="shared" ref="C21:C29" ca="1" si="2">RANDBETWEEN($C$32,$C$33)</f>
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="D21">
         <f t="shared" ref="D21:D29" ca="1" si="3">RANDBETWEEN(DB$15,$D$33)</f>
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <f t="shared" ref="E21:E29" ca="1" si="4">RANDBETWEEN($E$32,$E$33)/10</f>
@@ -1682,27 +1709,27 @@
       </c>
       <c r="F21">
         <f t="shared" ref="F21:F29" ca="1" si="5">RANDBETWEEN($F$32,$F$33)</f>
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="G21">
         <f t="shared" ref="G21:G29" ca="1" si="6">RANDBETWEEN($G$32,$G$33)</f>
-        <v>12</v>
+        <v>-14</v>
       </c>
       <c r="H21">
         <f t="shared" ref="H21:H29" ca="1" si="7">RANDBETWEEN($H$32,$H$33)</f>
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="I21">
         <f t="shared" ref="I21:I29" ca="1" si="8">RANDBETWEEN($I$32,$I$33)</f>
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <f t="shared" ref="J21:J29" ca="1" si="9">RANDBETWEEN($J$32,$J$33)/10</f>
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <f t="shared" ref="K21:K29" ca="1" si="10">RANDBETWEEN($K$32,$K$33)/10</f>
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -1711,62 +1738,62 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O21">
         <v>1.1000000000000001</v>
       </c>
       <c r="P21">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q21">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="0"/>
-        <v>120000</v>
+        <v>165000</v>
       </c>
       <c r="B22">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C22">
         <f t="shared" ca="1" si="2"/>
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="D22">
         <f t="shared" ca="1" si="3"/>
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F22">
         <f t="shared" ca="1" si="5"/>
-        <v>1</v>
+        <v>-13</v>
       </c>
       <c r="G22">
         <f t="shared" ca="1" si="6"/>
-        <v>-11</v>
+        <v>15</v>
       </c>
       <c r="H22">
         <f t="shared" ca="1" si="7"/>
-        <v>-18</v>
+        <v>-3</v>
       </c>
       <c r="I22">
         <f t="shared" ca="1" si="8"/>
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="J22">
         <f t="shared" ca="1" si="9"/>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="10"/>
-        <v>1.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -1775,62 +1802,52 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O22">
         <v>1.1000000000000001</v>
       </c>
       <c r="P22">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q22">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="0"/>
-        <v>126000</v>
+        <v>173250</v>
       </c>
       <c r="B23">
-        <f t="shared" ca="1" si="1"/>
-        <v>-78</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <f t="shared" ca="1" si="2"/>
-        <v>-138</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <f t="shared" ca="1" si="3"/>
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <f t="shared" ca="1" si="5"/>
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <f t="shared" ca="1" si="6"/>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <f t="shared" ca="1" si="8"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <f t="shared" ca="1" si="9"/>
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K23">
-        <f t="shared" ca="1" si="10"/>
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -1839,62 +1856,62 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O23">
         <v>1.1000000000000001</v>
       </c>
       <c r="P23">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q23">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="0"/>
-        <v>132000</v>
+        <v>181500</v>
       </c>
       <c r="B24">
         <f t="shared" ca="1" si="1"/>
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C24">
         <f t="shared" ca="1" si="2"/>
-        <v>-71</v>
+        <v>-150</v>
       </c>
       <c r="D24">
         <f t="shared" ca="1" si="3"/>
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E24">
         <f t="shared" ca="1" si="4"/>
-        <v>0.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F24">
         <f t="shared" ca="1" si="5"/>
-        <v>-8</v>
+        <v>2</v>
       </c>
       <c r="G24">
         <f t="shared" ca="1" si="6"/>
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H24">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="I24">
         <f t="shared" ca="1" si="8"/>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J24">
         <f t="shared" ca="1" si="9"/>
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K24">
         <f t="shared" ca="1" si="10"/>
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -1903,62 +1920,62 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O24">
         <v>1.1000000000000001</v>
       </c>
       <c r="P24">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q24">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25">
         <f t="shared" si="0"/>
-        <v>138000</v>
+        <v>189750</v>
       </c>
       <c r="B25">
         <f t="shared" ca="1" si="1"/>
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="C25">
         <f t="shared" ca="1" si="2"/>
-        <v>138</v>
+        <v>-26</v>
       </c>
       <c r="D25">
         <f t="shared" ca="1" si="3"/>
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="F25">
         <f t="shared" ca="1" si="5"/>
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="G25">
         <f t="shared" ca="1" si="6"/>
-        <v>-12</v>
+        <v>10</v>
       </c>
       <c r="H25">
         <f t="shared" ca="1" si="7"/>
-        <v>-9</v>
+        <v>4</v>
       </c>
       <c r="I25">
         <f t="shared" ca="1" si="8"/>
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="J25">
         <f t="shared" ca="1" si="9"/>
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K25">
         <f t="shared" ca="1" si="10"/>
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -1967,62 +1984,52 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>1.1000000000000001</v>
       </c>
       <c r="P25">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q25">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="0"/>
-        <v>144000</v>
+        <v>198000</v>
       </c>
       <c r="B26">
-        <f t="shared" ca="1" si="1"/>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <f t="shared" ca="1" si="2"/>
-        <v>-67</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <f t="shared" ca="1" si="3"/>
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <f t="shared" ca="1" si="4"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <f t="shared" ca="1" si="5"/>
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <f t="shared" ca="1" si="6"/>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <f t="shared" ca="1" si="7"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I26">
-        <f t="shared" ca="1" si="8"/>
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J26">
-        <f t="shared" ca="1" si="9"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="K26">
-        <f t="shared" ca="1" si="10"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2031,34 +2038,34 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O26">
         <v>1.1000000000000001</v>
       </c>
       <c r="P26">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q26">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="0"/>
-        <v>150000</v>
+        <v>206250</v>
       </c>
       <c r="B27">
         <f t="shared" ca="1" si="1"/>
-        <v>-76</v>
+        <v>-15</v>
       </c>
       <c r="C27">
         <f t="shared" ca="1" si="2"/>
-        <v>-143</v>
+        <v>-82</v>
       </c>
       <c r="D27">
         <f t="shared" ca="1" si="3"/>
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="E27">
         <f t="shared" ca="1" si="4"/>
@@ -2066,27 +2073,27 @@
       </c>
       <c r="F27">
         <f t="shared" ca="1" si="5"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <f t="shared" ca="1" si="6"/>
-        <v>-4</v>
+        <v>13</v>
       </c>
       <c r="H27">
         <f t="shared" ca="1" si="7"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <f t="shared" ca="1" si="8"/>
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="J27">
         <f t="shared" ca="1" si="9"/>
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="K27">
         <f t="shared" ca="1" si="10"/>
-        <v>1.1000000000000001</v>
+        <v>1</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -2095,62 +2102,62 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O27">
         <v>1.1000000000000001</v>
       </c>
       <c r="P27">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q27">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="0"/>
-        <v>156000</v>
+        <v>214500</v>
       </c>
       <c r="B28">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <f t="shared" ca="1" si="2"/>
-        <v>-155</v>
+        <v>-26</v>
       </c>
       <c r="D28">
         <f t="shared" ca="1" si="3"/>
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="E28">
         <f t="shared" ca="1" si="4"/>
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="F28">
         <f t="shared" ca="1" si="5"/>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="G28">
         <f t="shared" ca="1" si="6"/>
-        <v>-15</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <f t="shared" ca="1" si="7"/>
-        <v>14</v>
+        <v>-8</v>
       </c>
       <c r="I28">
         <f t="shared" ca="1" si="8"/>
-        <v>-14</v>
+        <v>-9</v>
       </c>
       <c r="J28">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K28">
         <f t="shared" ca="1" si="10"/>
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -2159,62 +2166,62 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O28">
         <v>1.1000000000000001</v>
       </c>
       <c r="P28">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q28">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29">
         <f t="shared" si="0"/>
-        <v>162000</v>
+        <v>222750</v>
       </c>
       <c r="B29">
         <f t="shared" ca="1" si="1"/>
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="C29">
         <f t="shared" ca="1" si="2"/>
-        <v>-150</v>
+        <v>95</v>
       </c>
       <c r="D29">
         <f t="shared" ca="1" si="3"/>
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="E29">
         <f t="shared" ca="1" si="4"/>
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F29">
         <f t="shared" ca="1" si="5"/>
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <f t="shared" ca="1" si="6"/>
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="H29">
         <f t="shared" ca="1" si="7"/>
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <f t="shared" ca="1" si="8"/>
-        <v>-18</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <f t="shared" ca="1" si="9"/>
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K29">
         <f t="shared" ca="1" si="10"/>
-        <v>1.5</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -2223,22 +2230,22 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>1.1000000000000001</v>
       </c>
       <c r="P29">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q29">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30">
         <f t="shared" si="0"/>
-        <v>168000</v>
+        <v>231000</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2277,24 +2284,24 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="O30">
         <v>1.1000000000000001</v>
       </c>
       <c r="P30">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q30">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>4125</v>
+        <v>8250</v>
       </c>
       <c r="B32">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="C32">
         <v>-180</v>
@@ -2303,7 +2310,7 @@
         <v>-180</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>-15</v>
@@ -2312,10 +2319,10 @@
         <v>-15</v>
       </c>
       <c r="H32">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="I32">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -2326,7 +2333,7 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C33">
         <v>180</v>
@@ -2344,10 +2351,10 @@
         <v>15</v>
       </c>
       <c r="H33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J33">
         <v>15</v>
